--- a/public/L'HOTE LORENTZ Léo - Tableau de synthese.xlsx
+++ b/public/L'HOTE LORENTZ Léo - Tableau de synthese.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BTS - 2ème Année\Stage et Examen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NevaOne\portfolio\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7968731-0902-44B7-9FF6-EA0286DD7B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5688D61F-537F-459D-8B87-D91835324360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -691,9 +691,27 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -711,24 +729,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1009,56 +1009,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="33"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1070,22 +1070,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="37" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1108,8 +1108,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
@@ -1130,16 +1130,16 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="47.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
@@ -1330,16 +1330,16 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
@@ -1474,22 +1474,22 @@
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
     </row>
     <row r="28" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C28" s="12"/>
@@ -1508,7 +1508,7 @@
       <c r="H28" s="18"/>
     </row>
     <row r="29" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="27" t="s">
         <v>47</v>
       </c>
       <c r="B29" s="19" t="s">
@@ -1679,11 +1679,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A4:E4"/>
@@ -1691,6 +1686,11 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
